--- a/data/b2_centro/B2 Centro 09-2026.xlsx
+++ b/data/b2_centro/B2 Centro 09-2026.xlsx
@@ -13,9 +13,9 @@
     <sheet name="DESPESAS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$109</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'MOVIMENTO DIÁRIO'!$A$1:$H$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'COMPRAS'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'DESPESAS'!$A$1:$D$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H109"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3720,8 +3720,344 @@
         <v>6.68</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>33500</v>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E110" s="9" t="n">
+        <v>6381</v>
+      </c>
+      <c r="F110" s="9" t="n">
+        <v>47113</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>5.7573</v>
+      </c>
+      <c r="H110" s="11" t="n">
+        <v>6.489</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C111" s="13" t="n">
+        <v>11405</v>
+      </c>
+      <c r="D111" s="13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E111" s="13" t="n">
+        <v>2910</v>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>23491</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>5.9046</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>6.78</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C112" s="9" t="n">
+        <v>16941</v>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E112" s="9" t="n">
+        <v>2949</v>
+      </c>
+      <c r="F112" s="9" t="n">
+        <v>38987</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>4.0035</v>
+      </c>
+      <c r="H112" s="11" t="n">
+        <v>4.585</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C113" s="13" t="n">
+        <v>10170</v>
+      </c>
+      <c r="D113" s="13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E113" s="13" t="n">
+        <v>2443</v>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>22723</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>6.0794</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>6.683</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C114" s="9" t="n">
+        <v>47113</v>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="9" t="n">
+        <v>6710</v>
+      </c>
+      <c r="F114" s="9" t="n">
+        <v>40402</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>5.7573</v>
+      </c>
+      <c r="H114" s="11" t="n">
+        <v>6.485</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C115" s="13" t="n">
+        <v>23491</v>
+      </c>
+      <c r="D115" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>3174</v>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>20316</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>5.9046</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>6.788</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="7" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>38987</v>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="9" t="n">
+        <v>3546</v>
+      </c>
+      <c r="F116" s="9" t="n">
+        <v>35434</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>4.0035</v>
+      </c>
+      <c r="H116" s="11" t="n">
+        <v>4.58</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C117" s="13" t="n">
+        <v>22723</v>
+      </c>
+      <c r="D117" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="13" t="n">
+        <v>2351</v>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>20372</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>6.0794</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>6.689</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n">
+        <v>40402</v>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="9" t="n">
+        <v>6199</v>
+      </c>
+      <c r="F118" s="9" t="n">
+        <v>34194</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>5.7573</v>
+      </c>
+      <c r="H118" s="11" t="n">
+        <v>6.479</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C119" s="13" t="n">
+        <v>20316</v>
+      </c>
+      <c r="D119" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="13" t="n">
+        <v>2894</v>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>17422</v>
+      </c>
+      <c r="G119" s="14" t="n">
+        <v>5.9046</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>6.778</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>35434</v>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="9" t="n">
+        <v>2761</v>
+      </c>
+      <c r="F120" s="9" t="n">
+        <v>32669</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>4.0035</v>
+      </c>
+      <c r="H120" s="11" t="n">
+        <v>4.583</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C121" s="13" t="n">
+        <v>20372</v>
+      </c>
+      <c r="D121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="13" t="n">
+        <v>2664</v>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>17702</v>
+      </c>
+      <c r="G121" s="14" t="n">
+        <v>6.0794</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>6.679</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H109"/>
+  <autoFilter ref="A1:H121"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -3737,7 +4073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4299,8 +4635,116 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Gasolina Comum</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>5.7649</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>115298.11</v>
+      </c>
+      <c r="F21" t="n">
+        <v>370839</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Distribuidora Sul</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Gasolina Aditivada</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>5.9101</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>88652.08</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>370850</v>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Distribuidora Sul</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Etanol</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>4.0131</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>100327.54</v>
+      </c>
+      <c r="F23" t="n">
+        <v>370862</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Distribuidora Sul</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Diesel S10</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>6.1002</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>91502.47</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>370869</v>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>Distribuidora Alfa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G24"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Gasolina Comum,Gasolina Aditivada,Etanol,Diesel S10"</formula1>
@@ -4316,7 +4760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4349,56 +4793,56 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46270</v>
+        <v>46268</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>76463.33</v>
+        <v>3551.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>4792.96</v>
+        <v>78348.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Coleta de resíduos (óleo e borra)</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2346.8</v>
+        <v>5034.73</v>
       </c>
     </row>
     <row r="5">
@@ -4439,20 +4883,20 @@
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reparo elétrico</t>
+          <t>Seguro do posto</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>2607.9</v>
+        <v>1263.92</v>
       </c>
     </row>
     <row r="8">
@@ -4461,52 +4905,52 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Seguro do posto</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>2254.45</v>
+        <v>2055.06</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>2027.53</v>
+        <v>5542.97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>6117.57</v>
+        <v>1537.88</v>
       </c>
     </row>
     <row r="11">
@@ -4524,7 +4968,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>12303.7</v>
+        <v>12806.73</v>
       </c>
     </row>
     <row r="12">
@@ -4533,52 +4977,52 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>3149.47</v>
+        <v>4087.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Material de limpeza e escritório</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>3891.92</v>
+        <v>1610.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Tarifas bancárias</t>
+          <t>Manutenção do compressor de ar</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>1475.1</v>
+        <v>3860.83</v>
       </c>
     </row>
     <row r="15">
@@ -4596,7 +5040,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>28015.33</v>
+        <v>27993.79</v>
       </c>
     </row>
     <row r="16">
@@ -4614,7 +5058,7 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>5927.33</v>
+        <v>5334.39</v>
       </c>
     </row>
     <row r="17">
@@ -4632,11 +5076,29 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>5700.04</v>
+        <v>6020.08</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Taxas de cartão</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Taxas das maquininhas (semana)</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>2524.87</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D17"/>
+  <autoFilter ref="A1:D18"/>
   <dataValidations count="1">
     <dataValidation sqref="B2:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list">
       <formula1>"Folha de pagamento,Aluguel,Energia elétrica,Água e esgoto,Taxas de cartão,Manutenção,Fretes,Sistemas e contabilidade,Marketing,Outras despesas"</formula1>
